--- a/DSA_Master_LeetCode_566_Updated.xlsx
+++ b/DSA_Master_LeetCode_566_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARMATRICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12F1D99-C808-4AC8-B872-0F56455B5023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6966CBE-B060-4FDC-942B-D627FAF1F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="1338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="1339">
   <si>
     <t>Sequence</t>
   </si>
@@ -4045,6 +4045,9 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/two-sum/submissions/2160251116/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/contains-duplicate/submissions/2160290124/</t>
   </si>
 </sst>
 </file>
@@ -4109,7 +4112,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4138,6 +4141,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4454,7 +4460,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="11" max="11" width="33.33203125" customWidth="1"/>
+    <col min="11" max="11" width="66" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4492,7 +4498,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -4556,9 +4562,11 @@
         <v>14</v>
       </c>
       <c r="J3" s="8">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>1338</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
@@ -23176,6 +23184,7 @@
   <autoFilter ref="A1:I567" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{634BCCE8-487A-4252-B66C-207045D8F449}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{7218A650-16F2-495A-8955-F257BF9D9F78}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DSA_Master_LeetCode_566_Updated.xlsx
+++ b/DSA_Master_LeetCode_566_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARMATRICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6966CBE-B060-4FDC-942B-D627FAF1F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8501A5ED-FBC6-4F86-B7BA-6CDD74E5EFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="1337">
   <si>
     <t>Sequence</t>
   </si>
@@ -4032,15 +4032,6 @@
     <t>Conplete</t>
   </si>
   <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
     <t>Solution Likn</t>
   </si>
   <si>
@@ -4048,13 +4039,16 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/contains-duplicate/submissions/2160290124/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-anagram/submissions/2161192603/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4072,6 +4066,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4139,11 +4140,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4495,7 +4496,7 @@
         <v>1332</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -4505,7 +4506,7 @@
       <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -4530,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -4540,7 +4541,7 @@
       <c r="B3" s="6">
         <v>217</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -4564,8 +4565,8 @@
       <c r="J3" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="11" t="s">
-        <v>1338</v>
+      <c r="K3" s="10" t="s">
+        <v>1335</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -4575,7 +4576,7 @@
       <c r="B4" s="6">
         <v>242</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="11" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -4597,9 +4598,11 @@
         <v>14</v>
       </c>
       <c r="J4" s="8">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
@@ -18924,25 +18927,25 @@
       <c r="K438" s="8"/>
     </row>
     <row r="439" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A439" s="10">
+      <c r="A439" s="7">
         <v>438</v>
       </c>
-      <c r="B439" s="10">
+      <c r="B439" s="7">
         <v>6</v>
       </c>
-      <c r="C439" s="10" t="s">
+      <c r="C439" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="D439" s="10" t="s">
+      <c r="D439" s="7" t="s">
         <v>1133</v>
       </c>
-      <c r="E439" s="10" t="s">
+      <c r="E439" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="F439" s="10" t="s">
+      <c r="F439" s="7" t="s">
         <v>1135</v>
       </c>
-      <c r="G439" s="10" t="s">
+      <c r="G439" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H439" s="7">
@@ -23185,6 +23188,7 @@
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{634BCCE8-487A-4252-B66C-207045D8F449}"/>
     <hyperlink ref="K3" r:id="rId2" xr:uid="{7218A650-16F2-495A-8955-F257BF9D9F78}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{0FDE3D88-2EDC-4439-9DCC-E7D58C87150B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
